--- a/Figures.xlsx
+++ b/Figures.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andres/Documents/GitHub/AMOC_Figures_Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3610D1E8-EB76-954B-8965-D0CF7DA9DCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD46DAD8-6444-D945-A90D-FA18FE504224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="4080" windowWidth="29200" windowHeight="14120" xr2:uid="{D6B1EF31-B44C-C14C-87F3-F58189DEBE44}"/>
+    <workbookView xWindow="920" yWindow="3500" windowWidth="29200" windowHeight="14120" xr2:uid="{D6B1EF31-B44C-C14C-87F3-F58189DEBE44}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="56">
   <si>
     <t>Chapter</t>
   </si>
@@ -201,6 +201,9 @@
   </si>
   <si>
     <t>Jon Robson</t>
+  </si>
+  <si>
+    <t>Antje Voelker</t>
   </si>
 </sst>
 </file>
@@ -661,6 +664,9 @@
       <c r="D4" t="s">
         <v>7</v>
       </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
       <c r="G4" t="s">
         <v>50</v>
       </c>

--- a/Figures.xlsx
+++ b/Figures.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andres/Documents/GitHub/AMOC_Figures_Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD46DAD8-6444-D945-A90D-FA18FE504224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214A9713-F2FF-C94F-AAD3-09A10E11BCAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="920" yWindow="3500" windowWidth="29200" windowHeight="14120" xr2:uid="{D6B1EF31-B44C-C14C-87F3-F58189DEBE44}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="66">
   <si>
     <t>Chapter</t>
   </si>
@@ -204,6 +204,36 @@
   </si>
   <si>
     <t>Antje Voelker</t>
+  </si>
+  <si>
+    <t>SPM</t>
+  </si>
+  <si>
+    <t>CRD</t>
+  </si>
+  <si>
+    <t>Siri Ellen Hallstrøm Eriksen</t>
+  </si>
+  <si>
+    <t>Illustrative climate resilient development (CRD) pathways for urban systems in Northern Europe as the Atlantic Meridional Overturning Circulation (AMOC) weakens. The blue window of opportunity shows that development options narrow over time with climate change and AMOC weakening and as constraints accumulate (pink). Immediate, ambitious mitigation and adaptation when integrated with sustainable development can transform urban systems. Any delay further narrows the window of opportunity after 2050 and entrenches pathways towards less sustainable outcomes. Due to lock-in, pathways towards higher CRD outcomes will be unavailable. The boxes on the right summarise CRD outcomes for urban systems in Northern Europe. It is urgent to put in place enabling conditions (below) to ensure early action that can keep open prospects for CRD.</t>
+  </si>
+  <si>
+    <t>The window for climate-resilient development (CRD) closes faster as the AMOC weakens. Reducing risks to urban populations in Northern Europe from a weakening AMOC depends on immediate, ambitious mitigation and adaptation, and from urban transformation.</t>
+  </si>
+  <si>
+    <t>Impacts</t>
+  </si>
+  <si>
+    <t>AMOC</t>
+  </si>
+  <si>
+    <t>Storylines</t>
+  </si>
+  <si>
+    <t>Maps</t>
+  </si>
+  <si>
+    <t>Mechanism</t>
   </si>
 </sst>
 </file>
@@ -563,9 +593,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41B8631-2699-4A47-96C1-316C80E1E97B}">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="3" max="3" width="24.33203125" customWidth="1"/>
     <col min="4" max="4" width="96.83203125" customWidth="1"/>
     <col min="5" max="5" width="27.33203125" customWidth="1"/>
   </cols>
@@ -1408,6 +1439,63 @@
         <v>0</v>
       </c>
     </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Figures.xlsx
+++ b/Figures.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="24.33203125" customWidth="1" min="3" max="3"/>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>The “conveyor belt” metaphor illustrates an intuitive view of large-scale ocean circulation and associated heat and carbon transport, but oversimplifies the underlying three-dimensional dynamics, including eddies, upwelling, and vertical mixing. The “tipping point” metaphor highlights the potential for abrupt and potentially irreversible transitions between system states, yet may mask the diversity of pathways, gradual changes, and uncertainties inherent in complex climate dynamics. These metaphors are therefore embedded within a broader framework of Earth system models, conceptual models, statistical analyses, observations, and proxy data, which provide the necessary physical grounding and quantification. The figure emphasizes that metaphors support insight and communication but must remain consistent with models, data, and associated uncertainties (cf. Lohmann, 2026).</t>
+          <t>Globally average near-surface air temperature (left axis) against AMOC strength (right axis). AMOC strength index is computed as the yearly average maximum of the meridional overturning streamfunction at 26.5°N below 500m. Only the first 100 years of the simulations are shown.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Globally average near-surface air temperature (left axis) against AMOC strength (right axis). AMOC strength index is computed as the yearly average maximum of the meridional overturning streamfunction at 26.5°N below 500m. Only the first 100 years of the simulations are shown.</t>
+          <t>Near-surface air temperature (over land) and sea surface temperature (over ocean). Left column: December-January-February (DJF); right column: June-July-August (JJA) seasonal mean changes between weak AMOC and fixed AMOC 4xCO2 experiments. Top row: 30% AMOC weakening; bottom row: 70% AMOC weakening. All temperature anomalies are normalized by climate sensitivity.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1401,7 +1401,7 @@
         <v>5</v>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Near-surface air temperature (over land) and sea surface temperature (over ocean). Left column: December-January-February (DJF); right column: June-July-August (JJA) seasonal mean changes between weak AMOC and fixed AMOC 4xCO2 experiments. Top row: 30% AMOC weakening; bottom row: 70% AMOC weakening. All temperature anomalies are normalized by climate sensitivity.</t>
+          <t>Precipitation (mm/day). Left column: December-January-February (DJF), right column: June-July-August (JJA) seasonal mean changes between weak AMOC and fixed AMOC 4xCO2 experiments. Top row: 30% AMOC weakening; bottom row: 70% AMOC weakening. All precipitation anomalies are normalized by climate sensitivity.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1429,10 +1429,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Precipitation (mm/day). Left column: December-January-February (DJF), right column: June-July-August (JJA) seasonal mean changes between weak AMOC and fixed AMOC 4xCO2 experiments. Top row: 30% AMOC weakening; bottom row: 70% AMOC weakening. All precipitation anomalies are normalized by climate sensitivity.</t>
+          <t>from: Hermans et al 2025. To explore how sea-level rise could be studied from an integrated perspective, we could adopt this figure and shape it more towards and AMOC weakening</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1463,7 +1463,7 @@
         <v>6</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>from: Hermans et al 2025. To explore how sea-level rise could be studied from an integrated perspective, we could adopt this figure and shape it more towards and AMOC weakening</t>
+          <t>Panel a: Geographically differentiated impacts, Panel b: Compounding and cascading risks driven by AMOC decline</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1494,7 +1494,7 @@
         <v>6</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Panel a: Geographically differentiated impacts, Panel b: Compounding and cascading risks driven by AMOC decline</t>
+          <t>Implications of AMOC futures for climate resilient development illustrated for policy makers. The illustrative development pathways (red to green) and associated outcomes (right panel) show that there is a rapidly narrowing window of opportunity to secure a liveable and sustainable future for all. Climate resilient development is the process of implementing greenhouse gas mitigation and adaptation measures to support sustainable development. Diverging pathways illustrate that interacting choices and actions made by diverse government, private sector and civil society actors can advance climate resilient development, shift pathways towards sustainability, and enable lower emissions and adaptation. Diverse knowledge and values include cultural values, Indigenous Knowledge, local knowledge, and scientific knowledge. Climatic and non-climatic events, such as droughts, floods or pandemics, pose more severe shocks to pathways with lower climate resilient development (red to yellow) than to pathways with higher climate resilient development (green). There are limits to adaptation and adaptive capacity for some human and natural systems at global warming of 1.5°C, and with every increment of warming, losses and damages will increase. The development pathways taken by countries at all stages of economic development impact GHG emissions and mitigation challenges and opportunities, which vary across countries and regions. Pathways and opportunities for action are shaped by previous actions (or inactions and opportunities missed; dashed pathway) and enabling and constraining conditions (left panel), and take place in the context of climate risks, adaptation limits and development gaps. The longer emissions reductions are delayed, the fewer effective adaptation options (Fig. 6.4 is reproduced with permission from Figure SPM.6 from the Summary for Policy Makers of the IPCC AR6 Synthesis Report)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1521,34 +1521,30 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>6</v>
-      </c>
-      <c r="B34" t="n">
-        <v>3</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SPM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CRD</t>
+        </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Placeholder intent.</t>
+          <t>The window for climate-resilient development (CRD) closes faster as the AMOC weakens. Reducing risks to urban populations in Northern Europe from a weakening AMOC depends on immediate, ambitious mitigation and adaptation, and from urban transformation.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Implications of AMOC futures for climate resilient development illustrated for policy makers. The illustrative development pathways (red to green) and associated outcomes (right panel) show that there is a rapidly narrowing window of opportunity to secure a liveable and sustainable future for all. Climate resilient development is the process of implementing greenhouse gas mitigation and adaptation measures to support sustainable development. Diverging pathways illustrate that interacting choices and actions made by diverse government, private sector and civil society actors can advance climate resilient development, shift pathways towards sustainability, and enable lower emissions and adaptation. Diverse knowledge and values include cultural values, Indigenous Knowledge, local knowledge, and scientific knowledge. Climatic and non-climatic events, such as droughts, floods or pandemics, pose more severe shocks to pathways with lower climate resilient development (red to yellow) than to pathways with higher climate resilient development (green). There are limits to adaptation and adaptive capacity for some human and natural systems at global warming of 1.5°C, and with every increment of warming, losses and damages will increase. The development pathways taken by countries at all stages of economic development impact GHG emissions and mitigation challenges and opportunities, which vary across countries and regions. Pathways and opportunities for action are shaped by previous actions (or inactions and opportunities missed; dashed pathway) and enabling and constraining conditions (left panel), and take place in the context of climate risks, adaptation limits and development gaps. The longer emissions reductions are delayed, the fewer effective adaptation options (Fig. 6.4 is reproduced with permission from Figure SPM.6 from the Summary for Policy Makers of the IPCC AR6 Synthesis Report)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>To add sources, leave them in the feedback. Andrés will then place them here.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>10.July</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
+          <t>Illustrative climate resilient development (CRD) pathways for urban systems in Northern Europe as the Atlantic Meridional Overturning Circulation (AMOC) weakens. The blue window of opportunity shows that development options narrow over time with climate change and AMOC weakening and as constraints accumulate (pink). Immediate, ambitious mitigation and adaptation when integrated with sustainable development can transform urban systems. Any delay further narrows the window of opportunity after 2050 and entrenches pathways towards less sustainable outcomes. Due to lock-in, pathways towards higher CRD outcomes will be unavailable. The boxes on the right summarise CRD outcomes for urban systems in Northern Europe. It is urgent to put in place enabling conditions (below) to ensure early action that can keep open prospects for CRD.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Siri Ellen Hallstrøm Eriksen</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1559,22 +1555,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CRD</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>The window for climate-resilient development (CRD) closes faster as the AMOC weakens. Reducing risks to urban populations in Northern Europe from a weakening AMOC depends on immediate, ambitious mitigation and adaptation, and from urban transformation.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Illustrative climate resilient development (CRD) pathways for urban systems in Northern Europe as the Atlantic Meridional Overturning Circulation (AMOC) weakens. The blue window of opportunity shows that development options narrow over time with climate change and AMOC weakening and as constraints accumulate (pink). Immediate, ambitious mitigation and adaptation when integrated with sustainable development can transform urban systems. Any delay further narrows the window of opportunity after 2050 and entrenches pathways towards less sustainable outcomes. Due to lock-in, pathways towards higher CRD outcomes will be unavailable. The boxes on the right summarise CRD outcomes for urban systems in Northern Europe. It is urgent to put in place enabling conditions (below) to ensure early action that can keep open prospects for CRD.</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Siri Ellen Hallstrøm Eriksen</t>
+          <t>Impacts</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1567,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Impacts</t>
+          <t>AMOC</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1579,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AMOC</t>
+          <t>Storylines</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1591,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Storylines</t>
+          <t>Maps</t>
         </is>
       </c>
     </row>
@@ -1621,18 +1602,6 @@
         </is>
       </c>
       <c r="B39" t="inlineStr">
-        <is>
-          <t>Maps</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>SPM</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
         <is>
           <t>Mechanism</t>
         </is>

--- a/Figures.xlsx
+++ b/Figures.xlsx
@@ -565,7 +565,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/Figures.xlsx
+++ b/Figures.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="24.33203125" customWidth="1" min="3" max="3"/>
@@ -565,36 +565,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cascading impacts on physical systems.
-The consequences of a substantial AMOC weakening reach beyond the Atlantic.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Impacts of strong AMOC decline and global warming on physical and biological systems in the Atlantic realm and through teleconnections to Asia. Figure adapted from (Collins et al., 2019).</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Antje Voelker</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>To add sources, leave them in the feedback. Andrés will then place them here.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>10.July</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
+          <t>AMOC strength at 26.5°N.
+SSP2-4.5, a moderate emissions scenario</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -602,48 +579,54 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cascading impacts on physical systems.
+The consequences of a substantial AMOC weakening reach beyond the Atlantic.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Impacts of strong AMOC decline and global warming on physical and biological systems in the Atlantic realm and through teleconnections to Asia. Figure adapted from (Collins et al., 2019).</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Antje Voelker</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>To add sources, leave them in the feedback. Andrés will then place them here.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>10.July</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
         <v>5</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Evaluation and communication of degree of certainty in findings.
 Each finding is stated as precisely as the evidence allows: from evidence and agreement, to confidence, to a likelihood where the evidence is quantitative.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Taken from Box 1.1 IPCC AR6 WGI (Chen et al., 2021). PLACEHOLDER FOR THE FIRST ORDER DRAFT:  Intend to change examples to be more relevant to AMOC report</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>To add sources, leave them in the feedback. Andrés will then place them here.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>10.July</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>The Atlantic Meridional Overturning Circulation (AMOC).</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Schematic map of the AMOC illustrating main currents, components, locations of key processes referred too, and perhaps where the evidence we describe is located. Note that Chapter 1 will create an AMOC schematic which we may be able to use as the base for our own map. Something like this (top) from (Chidichimo et al., 2023).</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -665,17 +648,16 @@
         <v>2</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Annual climatology for 1991–2020 across the Atlantic.
-Temperature and salinity averaged across the width of the Atlantic.</t>
+          <t>The Atlantic Meridional Overturning Circulation (AMOC).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">vertical slice like this from Lozier, 2012 </t>
+          <t>Schematic map of the AMOC illustrating main currents, components, locations of key processes referred too, and perhaps where the evidence we describe is located. Note that Chapter 1 will create an AMOC schematic which we may be able to use as the base for our own map. Something like this (top) from (Chidichimo et al., 2023).</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -697,16 +679,17 @@
         <v>2</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Placeholder intent.</t>
+          <t>Annual climatology for 1991–2020 across the Atlantic.
+Temperature and salinity averaged across the width of the Atlantic.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Interpreting climate records needs care and long records. I envisage a full SST time series (real), a new figure we make, but something like this from Zanchettin and Rubino, 2024. With long term trend overlaid or perhaps removed, then multidecadal trend picked out in a different colour (low pass filter), then a circle drawing attention to a multi-year period where the trend opposes the multidecadal trend (like 1950 to 1960 in the Atlantic multidecadal variability or the global Sea surface temperature, or 1980-85 in the Atlantic multidecadal variability. Maybe further circles highlighting peaks in individual years like 1879 or 1999 (or 2024 if we have a time series long enough). Link these circles to the sections of the paper for each timescale.</t>
+          <t xml:space="preserve">vertical slice like this from Lozier, 2012 </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -728,17 +711,16 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Timescales of AMOC variability.
-Observing arrays and reanalyses capture wind-driven changes and part of the buoyancy-driven ones. External forcing applies mostly on timescales that only models and proxies reach.</t>
+          <t>Placeholder intent.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Timescales of variability responding to forcing differs between basins (coloured bars, external applies to both basins), and sources of evidence for the state of the AMOC also cover very specific timescales. Adapted from Jackson et al., (2022) (here we suggest a modified version that may be more easily understood, but other suggestions are welcomed)</t>
+          <t>Interpreting climate records needs care and long records. I envisage a full SST time series (real), a new figure we make, but something like this from Zanchettin and Rubino, 2024. With long term trend overlaid or perhaps removed, then multidecadal trend picked out in a different colour (low pass filter), then a circle drawing attention to a multi-year period where the trend opposes the multidecadal trend (like 1950 to 1960 in the Atlantic multidecadal variability or the global Sea surface temperature, or 1980-85 in the Atlantic multidecadal variability. Maybe further circles highlighting peaks in individual years like 1879 or 1999 (or 2024 if we have a time series long enough). Link these circles to the sections of the paper for each timescale.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -760,17 +742,17 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The AMOC oceanic observing system.
-Parts of the Atlantic have been monitored since 1982, but the section network only became basin-wide in 2014.</t>
+          <t>Timescales of AMOC variability.
+Observing arrays and reanalyses capture wind-driven changes and part of the buoyancy-driven ones. External forcing applies mostly on timescales that only models and proxies reach.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Prepare a figure that includes the arrays and monitoring systems mentioned in the table</t>
+          <t>Timescales of variability responding to forcing differs between basins (coloured bars, external applies to both basins), and sources of evidence for the state of the AMOC also cover very specific timescales. Adapted from Jackson et al., (2022) (here we suggest a modified version that may be more easily understood, but other suggestions are welcomed)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,16 +774,17 @@
         <v>2</v>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placeholder intent.</t>
+          <t>The AMOC oceanic observing system.
+Parts of the Atlantic have been monitored since 1982, but the section network only became basin-wide in 2014.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ideally we would replot all these timeseries if we could get the data. Top left: Rossby et al., (2020). Nordic Seas AMOC. Top Right: Fraser and Cunningham )  subpolar AMOC. Middle left: Chafik et al., (2022) , Subpolar AMOC represented by the proxy of Irminger Sea upper ocean density. Middle Right: Caesar et al., (2018)   Sea surface temperature-based AMOC proxy, Bottom left Sea surface temperature  and  sea surface salinity proxies from Michel et al., (2025) supp mat., Bottom Right, Green is Machine Learning AMOC proxy from  Sea surface temperature and sea surface salinity at two selected (contrasting) latitudes (purple line is Caesar SPG  Sea surface temperature proxy and orange is   sea surface salinity proxy, both unchanged between the panels).</t>
+          <t>Prepare a figure that includes the arrays and monitoring systems mentioned in the table</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -823,7 +806,7 @@
         <v>2</v>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -832,12 +815,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Interglacial carbon isotope (δ13C) values measured in benthic foraminifera collected from sediment core IODP Site U1305 and MDXXXX collected from the Eirik Drift; southeast Greenland. MIS1 (0-7ka): red (Kleiven et al., 2008); MIS5 (116-123): blue (Galaasen et al., 2014); MIS7 (235-243): green; MIS9 (320-328): purple; MIS11 (395-415): yellow (Galaasen et al., 2020). High values at this location primarily reflect the production of well-ventilated Lower North Atlantic Deep Water   emanating from the Nordic Seas and a deep overturning cell in the subpolar North Atlantic.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Beyond its current vigor, the Holocene interglacial has also been exceptionally stable relative to the last half-million years. This unique stability is visually demonstrated through a histogram distribution of δ13C values (Fig. 2.7). </t>
+          <t>Ideally we would replot all these timeseries if we could get the data. Top left: Rossby et al., (2020). Nordic Seas AMOC. Top Right: Fraser and Cunningham )  subpolar AMOC. Middle left: Chafik et al., (2022) , Subpolar AMOC represented by the proxy of Irminger Sea upper ocean density. Middle Right: Caesar et al., (2018)   Sea surface temperature-based AMOC proxy, Bottom left Sea surface temperature  and  sea surface salinity proxies from Michel et al., (2025) supp mat., Bottom Right, Green is Machine Learning AMOC proxy from  Sea surface temperature and sea surface salinity at two selected (contrasting) latitudes (purple line is Caesar SPG  Sea surface temperature proxy and orange is   sea surface salinity proxy, both unchanged between the panels).</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -856,10 +834,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -868,7 +846,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Schematic of the Atlantic ocean circulation (simplified). In red the relatively warm surface flow is seen, in blue the cold deep water flow. The northward surface flow and southward deep flow together make up the Atlantic Meridional Overturning Circulation (AMOC). From Rahmstorf (1997)</t>
+          <t>Interglacial carbon isotope (δ13C) values measured in benthic foraminifera collected from sediment core IODP Site U1305 and MDXXXX collected from the Eirik Drift; southeast Greenland. MIS1 (0-7ka): red (Kleiven et al., 2008); MIS5 (116-123): blue (Galaasen et al., 2014); MIS7 (235-243): green; MIS9 (320-328): purple; MIS11 (395-415): yellow (Galaasen et al., 2020). High values at this location primarily reflect the production of well-ventilated Lower North Atlantic Deep Water   emanating from the Nordic Seas and a deep overturning cell in the subpolar North Atlantic.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beyond its current vigor, the Holocene interglacial has also been exceptionally stable relative to the last half-million years. This unique stability is visually demonstrated through a histogram distribution of δ13C values (Fig. 2.7). </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -890,7 +873,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -899,12 +882,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CMIP6 annual mean Atlantic Meridional Overturning Circulation (AMOC) strength percentage change in anomalies against 1950-2000 baseline period (top) and absolute values (bottom) of AMOC index,  calculated for each ensemble member as maxima at 26N over the entire depth for annual mean meridional overturning mass streamfunction (msfmz/msftyz) across the historical, SSP1-1.9, SSP1-2.6, SSP2-4.5, SSP3-7.0 and SSP5-8.5 scenarios. The circles to the right of the panel show the values averaged from 2081–2100 for each of the available model simulations.</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>Gaurav Madan</t>
+          <t>Schematic of the Atlantic ocean circulation (simplified). In red the relatively warm surface flow is seen, in blue the cold deep water flow. The northward surface flow and southward deep flow together make up the Atlantic Meridional Overturning Circulation (AMOC). From Rahmstorf (1997)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -926,7 +904,7 @@
         <v>3</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -935,7 +913,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CMIP6 annual mean maximum Atlantic Meridional Overturning Circulation (AMOC) strength percentage change at 26N in historical and scenario simulations. The changes are relative to averages from 1950–2000 for each model across the historical, SSP1-2.6, SSP2-4.5, and SSP5-8.5 scenarios. The thick grey line denotes the multi-model mean for the historical simulation, while the thick coloured lines denote the corresponding multi-model means for SSP1-2.6, SSP2-4.5 and SSP5-8.5. Multi-model means are computed after individual model means are computed first. Thin lines show the evolution of each individual member. The circles to the right of the panel show the change averaged from 2281–2300 for each of the available ensemble member.</t>
+          <t>CMIP6 annual mean Atlantic Meridional Overturning Circulation (AMOC) strength percentage change in anomalies against 1950-2000 baseline period (top) and absolute values (bottom) of AMOC index,  calculated for each ensemble member as maxima at 26N over the entire depth for annual mean meridional overturning mass streamfunction (msfmz/msftyz) across the historical, SSP1-1.9, SSP1-2.6, SSP2-4.5, SSP3-7.0 and SSP5-8.5 scenarios. The circles to the right of the panel show the values averaged from 2081–2100 for each of the available model simulations.</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
@@ -962,16 +940,21 @@
         <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>The AMOC regional components and observing system</t>
+          <t>Placeholder intent.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Schematic of the horizontal circulation in the North Atlantic and Arctic Mediterranean. The Polar Water (cyan) lies at the surface, the North Atlantic Deep Water (blue) lies at depth, and the Atlantic Water from the North Atlantic Current lies at the surface in the Atlantic and Nordic Seas and at intermediate depth in the Arctic Ocean (red and pink). The Rapid Climate Change (RAPID) and Overturning in the Subpolar North Atlantic Program (OSNAP) arrays are shown with black dots. The background color is sea surface temperature. BS = Bering Strait. CAA = Canadian Arctic Archipelago. FS = Fram Strait. BSO = Barents Sea Opening. DaS = Davis Strait. DeS = Denmark Strait. GSR = Greenland-Scotland Ridge. NAC = North Atlantic Current. From Weijer et al. (2020).</t>
+          <t>CMIP6 annual mean maximum Atlantic Meridional Overturning Circulation (AMOC) strength percentage change at 26N in historical and scenario simulations. The changes are relative to averages from 1950–2000 for each model across the historical, SSP1-2.6, SSP2-4.5, and SSP5-8.5 scenarios. The thick grey line denotes the multi-model mean for the historical simulation, while the thick coloured lines denote the corresponding multi-model means for SSP1-2.6, SSP2-4.5 and SSP5-8.5. Multi-model means are computed after individual model means are computed first. Thin lines show the evolution of each individual member. The circles to the right of the panel show the change averaged from 2281–2300 for each of the available ensemble member.</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Gaurav Madan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -993,16 +976,16 @@
         <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Placeholder intent.</t>
+          <t>The AMOC regional components and observing system</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sensitivity of the Atlantic Meridional Overturning Circulation to model resolution. (a) The annual-mean AMOC strength at 26N in a high-resolution (red line) and low-resolution (blue line) version of the CESM1.3 model, defined as the maximum of the overturning streamfunction. AMOC estimates from the RAPID array, from satellite altimetry and cable measurements (Frajka-Williams 2015), and from the GloSea5 reanalysis (Jackson et al. 2016) are also shown. (b),(c) Linear decadal trends between 1950–2100 in AMOC strength for the high-resolution and low-resolution simulation. The solid magenta contours denote the long-term mean stream functions. Figure from Gou et al. (2024).</t>
+          <t>Schematic of the horizontal circulation in the North Atlantic and Arctic Mediterranean. The Polar Water (cyan) lies at the surface, the North Atlantic Deep Water (blue) lies at depth, and the Atlantic Water from the North Atlantic Current lies at the surface in the Atlantic and Nordic Seas and at intermediate depth in the Arctic Ocean (red and pink). The Rapid Climate Change (RAPID) and Overturning in the Subpolar North Atlantic Program (OSNAP) arrays are shown with black dots. The background color is sea surface temperature. BS = Bering Strait. CAA = Canadian Arctic Archipelago. FS = Fram Strait. BSO = Barents Sea Opening. DaS = Davis Strait. DeS = Denmark Strait. GSR = Greenland-Scotland Ridge. NAC = North Atlantic Current. From Weijer et al. (2020).</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1024,7 +1007,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1033,7 +1016,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time series of the change in AMOC strength for GCMs participating in CMIP6 under SSP1-2.6 (a), SSP2-4.5 (b) and SSP5-8.5 (c) emissions scenarios. The thick lines denote the averages of the four GCMs with the strongest present-day AMOC (red), the four GCMs with the weakest present-day AMOC (blue) and all GCMs (black). Each thin line denotes an individual GCM. The start year in a–c is 2015. </t>
+          <t>Sensitivity of the Atlantic Meridional Overturning Circulation to model resolution. (a) The annual-mean AMOC strength at 26N in a high-resolution (red line) and low-resolution (blue line) version of the CESM1.3 model, defined as the maximum of the overturning streamfunction. AMOC estimates from the RAPID array, from satellite altimetry and cable measurements (Frajka-Williams 2015), and from the GloSea5 reanalysis (Jackson et al. 2016) are also shown. (b),(c) Linear decadal trends between 1950–2100 in AMOC strength for the high-resolution and low-resolution simulation. The solid magenta contours denote the long-term mean stream functions. Figure from Gou et al. (2024).</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1055,7 +1038,7 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1064,7 +1047,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>From Portmann et al., 2026. Impact of each observable variable of (A) sea surface salinity (SSS) and (B) sea surface temperature (SST) on the constrained estimate of the future AMOC. The constraint based on ridge-regularised linear regression corrects the unconstrained estimate of the future AMOC. This correction is decomposed for each of the observable variables and shown here in colour. The two most important groups of observable variables are salinity in the South Atlantic and temperature in the subtropical region.</t>
+          <t xml:space="preserve">Time series of the change in AMOC strength for GCMs participating in CMIP6 under SSP1-2.6 (a), SSP2-4.5 (b) and SSP5-8.5 (c) emissions scenarios. The thick lines denote the averages of the four GCMs with the strongest present-day AMOC (red), the four GCMs with the weakest present-day AMOC (blue) and all GCMs (black). Each thin line denotes an individual GCM. The start year in a–c is 2015. </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1086,7 +1069,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1095,12 +1078,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">shows a [DRAFT] causal network to represent the key processes associated with a decline of the subtropical AMOC. [NOTE this just attempts to show the mean state for now. It is probably too complicated and still needs to include climate change and how that affects the network. We also plan to use the network to additionally indicate where we think the major uncertainties are in the links between the nodes. Comments welcome.] </t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>Jon Robson</t>
+          <t>From Portmann et al., 2026. Impact of each observable variable of (A) sea surface salinity (SSS) and (B) sea surface temperature (SST) on the constrained estimate of the future AMOC. The constraint based on ridge-regularised linear regression corrects the unconstrained estimate of the future AMOC. This correction is decomposed for each of the observable variables and shown here in colour. The two most important groups of observable variables are salinity in the South Atlantic and temperature in the subtropical region.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1119,10 +1097,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1131,7 +1109,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Conceptual triangle of evidence for AMOC tipping. A schematic framework organizing the three principal lines of evidence for Atlantic Meridional Overturning Circulation (AMOC) tipping: conceptual theory, numerical models, and paleoclimate evidence. Conceptual theory provides the mechanistic foundation for bistability, thresholds, and hysteresis through density-driven feedbacks, particularly the salt–advection feedback. Numerical models, ranging from idealized box models to comprehensive Earth system models, test these mechanisms under controlled and realistic forcing scenarios. Paleoclimate records provide empirical evidence that abrupt reorganizations of the overturning circulation have occurred in the past. Together, these approaches establish the physical plausibility of AMOC tipping. However, discrepancies among them—most notably between conceptual and paleoclimate indications of bistability and the generally gradual response simulated by comprehensive climate models—highlight persistent uncertainty regarding the likelihood of a transition under present-day anthropogenic forcing.</t>
+          <t xml:space="preserve">shows a [DRAFT] causal network to represent the key processes associated with a decline of the subtropical AMOC. [NOTE this just attempts to show the mean state for now. It is probably too complicated and still needs to include climate change and how that affects the network. We also plan to use the network to additionally indicate where we think the major uncertainties are in the links between the nodes. Comments welcome.] </t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>Jon Robson</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1153,17 +1136,16 @@
         <v>4</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Three mechanisms of tipping in the AMOC system.
-The AMOC could tip when forcing crosses a critical threshold, but also below it: through internal variability, or when forcing changes faster than the circulation can adjust.</t>
+          <t>Placeholder intent.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Three mechanisms of tipping in the AMOC system. Schematic illustration of the three principal types of tipping behavior and their relevance for Atlantic Meridional Overturning Circulation (AMOC) dynamics, inspired by Ashwin et al. (2012).  Bifurcation-induced tipping (left) occurs when gradual changes in forcing—such as sustained freshwater input from Greenland melt, Arctic freshwater input or enhanced precipitation—push the system across a critical threshold, beyond which the vigorous overturning state becomes unstable and transitions to a weak or collapsed mode. Noise-induced tipping (middle) arises when internal variability in ocean–atmosphere dynamics drives the system across the boundary of its basin of attraction, implying that abrupt AMOC transitions can occur probabilistically even under moderate forcing. Rate-induced tipping (right) occurs when rapid changes in forcing—such as abrupt freshwater pulses or rapid warming—outpace the system’s adjustment, leading to a departure from equilibrium and potentially triggering an irreversible shift. Dashed lines indicate critical thresholds or reference states, while trajectories illustrate possible system responses. Together, these mechanisms highlight that AMOC stability is governed not only by the magnitude of forcing, but also by its temporal variability and rate of change, with important implications for assessing tipping risk under future climate scenarios.</t>
+          <t>Conceptual triangle of evidence for AMOC tipping. A schematic framework organizing the three principal lines of evidence for Atlantic Meridional Overturning Circulation (AMOC) tipping: conceptual theory, numerical models, and paleoclimate evidence. Conceptual theory provides the mechanistic foundation for bistability, thresholds, and hysteresis through density-driven feedbacks, particularly the salt–advection feedback. Numerical models, ranging from idealized box models to comprehensive Earth system models, test these mechanisms under controlled and realistic forcing scenarios. Paleoclimate records provide empirical evidence that abrupt reorganizations of the overturning circulation have occurred in the past. Together, these approaches establish the physical plausibility of AMOC tipping. However, discrepancies among them—most notably between conceptual and paleoclimate indications of bistability and the generally gradual response simulated by comprehensive climate models—highlight persistent uncertainty regarding the likelihood of a transition under present-day anthropogenic forcing.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1185,17 +1167,17 @@
         <v>4</v>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Physical mechanisms governing AMOC stability.
-Heat loss, freshwater input and sea-ice processes regulate how much deep water forms in the north. The balance between feedbacks decides whether a disturbance is damped or amplified.</t>
+          <t>Three mechanisms of tipping in the AMOC system.
+The AMOC could tip when forcing crosses a critical threshold, but also below it: through internal variability, or when forcing changes faster than the circulation can adjust.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Physical mechanisms governing AMOC stability. Schematic overview of the key physical processes controlling the stability of the Atlantic Meridional Overturning Circulation (AMOC). Surface buoyancy forcing—through heat loss, freshwater input, and sea-ice processes—regulates deep-water formation in the Labrador, Irminger, and Nordic Seas. Convective processes interact with advective salt transport, whereby changes in overturning strength modify northward salinity fluxes, giving rise to the salt–advection feedback. Subpolar gyre circulation redistributes salinity anomalies and can either stabilize or destabilize the system. Overflows across the Greenland–Scotland Ridge contribute to the lower limb of the circulation, while Southern Ocean upwelling links the AMOC to global overturning. Atmospheric feedbacks, including freshwater export from the Atlantic basin, further modulate stability. The balance between these interacting processes determines whether perturbations are damped or amplified.</t>
+          <t>Three mechanisms of tipping in the AMOC system. Schematic illustration of the three principal types of tipping behavior and their relevance for Atlantic Meridional Overturning Circulation (AMOC) dynamics, inspired by Ashwin et al. (2012).  Bifurcation-induced tipping (left) occurs when gradual changes in forcing—such as sustained freshwater input from Greenland melt, Arctic freshwater input or enhanced precipitation—push the system across a critical threshold, beyond which the vigorous overturning state becomes unstable and transitions to a weak or collapsed mode. Noise-induced tipping (middle) arises when internal variability in ocean–atmosphere dynamics drives the system across the boundary of its basin of attraction, implying that abrupt AMOC transitions can occur probabilistically even under moderate forcing. Rate-induced tipping (right) occurs when rapid changes in forcing—such as abrupt freshwater pulses or rapid warming—outpace the system’s adjustment, leading to a departure from equilibrium and potentially triggering an irreversible shift. Dashed lines indicate critical thresholds or reference states, while trajectories illustrate possible system responses. Together, these mechanisms highlight that AMOC stability is governed not only by the magnitude of forcing, but also by its temporal variability and rate of change, with important implications for assessing tipping risk under future climate scenarios.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1217,17 +1199,17 @@
         <v>4</v>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Placeholder intent.</t>
+          <t>Physical mechanisms governing AMOC stability.
+Heat loss, freshwater input and sea-ice processes regulate how much deep water forms in the north. The balance between feedbacks decides whether a disturbance is damped or amplified.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Regional and small-scale restructuring of the AMOC under global warming. 
-Summary of the spatially heterogeneous response of the Atlantic Meridional Overturning Circulation (AMOC) to global warming, based on high-resolution climate model simulations (Gou et al., 2024). While the basin-scale AMOC index exhibits a relatively smooth decline, regional overturning and small-scale processes—including deep convection and mesoscale eddy activity—undergo abrupt and non-uniform changes. In particular, convection in the eastern subpolar North Atlantic weakens rapidly and can nearly cease, while overturning north of the Greenland–Scotland Ridge strengthens in association with sea-ice retreat and enhanced mixing. These regional changes are closely linked to shifts in eddy activity and density structure, which redistribute freshwater and modify stratification. High-resolution simulations reveal pronounced spatial contrasts and step-like transitions that are absent in coarse-resolution models, highlighting that small-scale processes can exhibit tipping-like behavior even when the large-scale AMOC evolves gradually. This implies that the AMOC should be interpreted as a superposition of interacting regional components with distinct sensitivities and potential thresholds, rather than as a single coherent overturning mode.</t>
+          <t>Physical mechanisms governing AMOC stability. Schematic overview of the key physical processes controlling the stability of the Atlantic Meridional Overturning Circulation (AMOC). Surface buoyancy forcing—through heat loss, freshwater input, and sea-ice processes—regulates deep-water formation in the Labrador, Irminger, and Nordic Seas. Convective processes interact with advective salt transport, whereby changes in overturning strength modify northward salinity fluxes, giving rise to the salt–advection feedback. Subpolar gyre circulation redistributes salinity anomalies and can either stabilize or destabilize the system. Overflows across the Greenland–Scotland Ridge contribute to the lower limb of the circulation, while Southern Ocean upwelling links the AMOC to global overturning. Atmospheric feedbacks, including freshwater export from the Atlantic basin, further modulate stability. The balance between these interacting processes determines whether perturbations are damped or amplified.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1249,7 +1231,7 @@
         <v>4</v>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1258,7 +1240,8 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Summary of abrupt climate events linked to changes in the Atlantic Meridional Overturning Circulation (AMOC), including Heinrich event 1 (H1), the Younger Dryas (YD), and the 8.2 ka event. These events demonstrate that the AMOC can reorganize rapidly on decadal to centennial timescales in response to freshwater perturbations, iceberg discharge, and sea-ice feedbacks. Heinrich events represent large-scale, basin-wide freshwater forcing associated with iceberg rafting, whereas the Younger Dryas and 8.2 ka event are linked to more localized or routed freshwater inputs. This distinction highlights that not only the magnitude but also the spatial distribution and pathway of freshwater forcing influence the AMOC response, providing a direct link to the mechanisms illustrated in Fig. 6. Although past boundary conditions differ from the present, these records demonstrate the inherent capacity of the AMOC for abrupt transitions and constrain the range of possible responses under future climate forcing.   [PLACEHOLDER FOR FIRST ORDER DRAFT]</t>
+          <t>Regional and small-scale restructuring of the AMOC under global warming. 
+Summary of the spatially heterogeneous response of the Atlantic Meridional Overturning Circulation (AMOC) to global warming, based on high-resolution climate model simulations (Gou et al., 2024). While the basin-scale AMOC index exhibits a relatively smooth decline, regional overturning and small-scale processes—including deep convection and mesoscale eddy activity—undergo abrupt and non-uniform changes. In particular, convection in the eastern subpolar North Atlantic weakens rapidly and can nearly cease, while overturning north of the Greenland–Scotland Ridge strengthens in association with sea-ice retreat and enhanced mixing. These regional changes are closely linked to shifts in eddy activity and density structure, which redistribute freshwater and modify stratification. High-resolution simulations reveal pronounced spatial contrasts and step-like transitions that are absent in coarse-resolution models, highlighting that small-scale processes can exhibit tipping-like behavior even when the large-scale AMOC evolves gradually. This implies that the AMOC should be interpreted as a superposition of interacting regional components with distinct sensitivities and potential thresholds, rather than as a single coherent overturning mode.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1280,7 +1263,7 @@
         <v>4</v>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1289,7 +1272,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Schematic illustration of how the Atlantic Meridional Overturning Circulation (AMOC) responds to different freshwater forcing geometries, informed by model experiments and paleoclimate reconstructions. (a) Coastal freshwater input, analogous to the 8.2 ka event, is routed along continental margins and remains largely confined to boundary currents, producing localized stratification and a moderate, often reversible weakening of the AMOC (Condron and Winsor, 2012; Lohmann et al., 2020). (b) Subpolar or open-ocean freshwater forcing, characteristic of Heinrich events, is distributed across the North Atlantic and directly impacts deep convection regions, leading to stronger stratification and pronounced reductions in overturning (Hill and Condron, 2014; Condron and Hill, 2021). (c) Model resolution strongly modulates these responses: coarse-resolution models tend to overmix freshwater anomalies and exaggerate their impact on deep convection, whereas high-resolution models better resolve boundary currents, eddies, and freshwater pathways, allowing anomalies to remain confined and reducing their influence on basin-scale overturning. These results demonstrate that AMOC sensitivity depends not only on freshwater magnitude, but also on its spatial distribution, routing, and representation in models.    </t>
+          <t>Summary of abrupt climate events linked to changes in the Atlantic Meridional Overturning Circulation (AMOC), including Heinrich event 1 (H1), the Younger Dryas (YD), and the 8.2 ka event. These events demonstrate that the AMOC can reorganize rapidly on decadal to centennial timescales in response to freshwater perturbations, iceberg discharge, and sea-ice feedbacks. Heinrich events represent large-scale, basin-wide freshwater forcing associated with iceberg rafting, whereas the Younger Dryas and 8.2 ka event are linked to more localized or routed freshwater inputs. This distinction highlights that not only the magnitude but also the spatial distribution and pathway of freshwater forcing influence the AMOC response, providing a direct link to the mechanisms illustrated in Fig. 6. Although past boundary conditions differ from the present, these records demonstrate the inherent capacity of the AMOC for abrupt transitions and constrain the range of possible responses under future climate forcing.   [PLACEHOLDER FOR FIRST ORDER DRAFT]</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1308,10 +1291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1320,7 +1303,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Globally average near-surface air temperature (left axis) against AMOC strength (right axis). AMOC strength index is computed as the yearly average maximum of the meridional overturning streamfunction at 26.5°N below 500m. Only the first 100 years of the simulations are shown.</t>
+          <t xml:space="preserve">Schematic illustration of how the Atlantic Meridional Overturning Circulation (AMOC) responds to different freshwater forcing geometries, informed by model experiments and paleoclimate reconstructions. (a) Coastal freshwater input, analogous to the 8.2 ka event, is routed along continental margins and remains largely confined to boundary currents, producing localized stratification and a moderate, often reversible weakening of the AMOC (Condron and Winsor, 2012; Lohmann et al., 2020). (b) Subpolar or open-ocean freshwater forcing, characteristic of Heinrich events, is distributed across the North Atlantic and directly impacts deep convection regions, leading to stronger stratification and pronounced reductions in overturning (Hill and Condron, 2014; Condron and Hill, 2021). (c) Model resolution strongly modulates these responses: coarse-resolution models tend to overmix freshwater anomalies and exaggerate their impact on deep convection, whereas high-resolution models better resolve boundary currents, eddies, and freshwater pathways, allowing anomalies to remain confined and reducing their influence on basin-scale overturning. These results demonstrate that AMOC sensitivity depends not only on freshwater magnitude, but also on its spatial distribution, routing, and representation in models.    </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1342,7 +1325,7 @@
         <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1351,7 +1334,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Near-surface air temperature (over land) and sea surface temperature (over ocean). Left column: December-January-February (DJF); right column: June-July-August (JJA) seasonal mean changes between weak AMOC and fixed AMOC 4xCO2 experiments. Top row: 30% AMOC weakening; bottom row: 70% AMOC weakening. All temperature anomalies are normalized by climate sensitivity.</t>
+          <t>Globally average near-surface air temperature (left axis) against AMOC strength (right axis). AMOC strength index is computed as the yearly average maximum of the meridional overturning streamfunction at 26.5°N below 500m. Only the first 100 years of the simulations are shown.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1373,7 +1356,7 @@
         <v>5</v>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1382,7 +1365,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Precipitation (mm/day). Left column: December-January-February (DJF), right column: June-July-August (JJA) seasonal mean changes between weak AMOC and fixed AMOC 4xCO2 experiments. Top row: 30% AMOC weakening; bottom row: 70% AMOC weakening. All precipitation anomalies are normalized by climate sensitivity.</t>
+          <t>Near-surface air temperature (over land) and sea surface temperature (over ocean). Left column: December-January-February (DJF); right column: June-July-August (JJA) seasonal mean changes between weak AMOC and fixed AMOC 4xCO2 experiments. Top row: 30% AMOC weakening; bottom row: 70% AMOC weakening. All temperature anomalies are normalized by climate sensitivity.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1401,10 +1384,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1413,7 +1396,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>from: Hermans et al 2025. To explore how sea-level rise could be studied from an integrated perspective, we could adopt this figure and shape it more towards and AMOC weakening</t>
+          <t>Precipitation (mm/day). Left column: December-January-February (DJF), right column: June-July-August (JJA) seasonal mean changes between weak AMOC and fixed AMOC 4xCO2 experiments. Top row: 30% AMOC weakening; bottom row: 70% AMOC weakening. All precipitation anomalies are normalized by climate sensitivity.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1435,17 +1418,16 @@
         <v>6</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Risks of a substantial and irreversible AMOC weakening.
-Single regional failures could have global impacts through food commodity markets that transmit shocks as prices spikes.</t>
+          <t>Placeholder intent.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Panel a: Geographically differentiated impacts, Panel b: Compounding and cascading risks driven by AMOC decline</t>
+          <t>from: Hermans et al 2025. To explore how sea-level rise could be studied from an integrated perspective, we could adopt this figure and shape it more towards and AMOC weakening</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1467,145 +1449,177 @@
         <v>6</v>
       </c>
       <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Risks of a substantial and irreversible AMOC weakening.
+Single regional failures could have global impacts through food commodity markets that transmit shocks as prices spikes.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Panel a: Geographically differentiated impacts, Panel b: Compounding and cascading risks driven by AMOC decline</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>To add sources, leave them in the feedback. Andrés will then place them here.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>10.July</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" t="n">
         <v>3</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>The window for climate-resilient development (CRD) closes faster as the AMOC weakens.
 Illustrating how reducing risks to urban populations in Northern Europe from a weakening AMOC depends on immediate, ambitious mitigation and adaptation, and from urban transformation.</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Implications of AMOC futures for climate resilient development illustrated for policy makers. The illustrative development pathways (red to green) and associated outcomes (right panel) show that there is a rapidly narrowing window of opportunity to secure a liveable and sustainable future for all. Climate resilient development is the process of implementing greenhouse gas mitigation and adaptation measures to support sustainable development. Diverging pathways illustrate that interacting choices and actions made by diverse government, private sector and civil society actors can advance climate resilient development, shift pathways towards sustainability, and enable lower emissions and adaptation. Diverse knowledge and values include cultural values, Indigenous Knowledge, local knowledge, and scientific knowledge. Climatic and non-climatic events, such as droughts, floods or pandemics, pose more severe shocks to pathways with lower climate resilient development (red to yellow) than to pathways with higher climate resilient development (green). There are limits to adaptation and adaptive capacity for some human and natural systems at global warming of 1.5°C, and with every increment of warming, losses and damages will increase. The development pathways taken by countries at all stages of economic development impact GHG emissions and mitigation challenges and opportunities, which vary across countries and regions. Pathways and opportunities for action are shaped by previous actions (or inactions and opportunities missed; dashed pathway) and enabling and constraining conditions (left panel), and take place in the context of climate risks, adaptation limits and development gaps. The longer emissions reductions are delayed, the fewer effective adaptation options (Fig. 6.4 is reproduced with permission from Figure SPM.6 from the Summary for Policy Makers of the IPCC AR6 Synthesis Report)</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>To add sources, leave them in the feedback. Andrés will then place them here.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>10.July</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>To add sources, leave them in the feedback. Andrés will then place them here.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>10.July</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>SPM</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>CRD</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>The window for climate-resilient development (CRD) closes faster as the AMOC weakens.
 Illustrating how reducing risks to urban populations in Northern Europe from a weakening AMOC depends on immediate, ambitious mitigation and adaptation, and from urban transformation.</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Illustrative climate resilient development (CRD) pathways for urban systems in Northern Europe as the Atlantic Meridional Overturning Circulation (AMOC) weakens. The blue window of opportunity shows that development options narrow over time with climate change and AMOC weakening and as constraints accumulate (pink). Immediate, ambitious mitigation and adaptation when integrated with sustainable development can transform urban systems. Any delay further narrows the window of opportunity after 2050 and entrenches pathways towards less sustainable outcomes. Due to lock-in, pathways towards higher CRD outcomes will be unavailable. The boxes on the right summarise CRD outcomes for urban systems in Northern Europe. It is urgent to put in place enabling conditions (below) to ensure early action that can keep open prospects for CRD.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Siri Ellen Hallstrøm Eriksen</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>SPM</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Impacts</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Cascading impacts on biophysical and human systems.
 The consequences of a substantial and irreversible AMOC weakening reach far beyond the Atlantic, and propagate from biophysical systems to human ones.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>SPM</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>AMOC</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>The Atlantic Meridional Overturning Circulation (AMOC).
 The AMOC is a system of connected regional components, not a one current belt.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>SPM</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Storylines</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Where we are coming from, and the paths ahead.
 Steady for 10,000 years, measured for twenty, and projected to weaken.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>SPM</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Maps</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Regional climate response to a weakening AMOC.
 A weakening AMOC cools the North Atlantic and Europe and shifts tropical rainfall southward, a pattern distinct from, and in places opposite to, greenhouse-gas-driven change.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>SPM</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Mechanism</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Mechanisms setting the strength of the AMOC.
 Freshwater and warming both reduce the dense water that drives the circulation; wind sustains part of it whatever happens to density. Two feedbacks pull in opposite directions.</t>

--- a/Figures.xlsx
+++ b/Figures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andres/Documents/GitHub/AMOC_Figures_Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE2C2F0-29D0-6049-9591-099712BB78EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F0D35D-61D7-0B4B-A232-8AED600C4645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="920" yWindow="3500" windowWidth="29200" windowHeight="14120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="80">
   <si>
     <t>Chapter</t>
   </si>
@@ -199,9 +199,6 @@
     <t>Precipitation (mm/day). Left column: December-January-February (DJF), right column: June-July-August (JJA) seasonal mean changes between weak AMOC and fixed AMOC 4xCO2 experiments. Top row: 30% AMOC weakening; bottom row: 70% AMOC weakening. All precipitation anomalies are normalized by climate sensitivity.</t>
   </si>
   <si>
-    <t>from: Hermans et al 2025. To explore how sea-level rise could be studied from an integrated perspective, we could adopt this figure and shape it more towards and AMOC weakening</t>
-  </si>
-  <si>
     <t>Risks of a substantial and irreversible AMOC weakening.
 Single regional failures could have global impacts through food commodity markets that transmit shocks as prices spikes.</t>
   </si>
@@ -276,6 +273,9 @@
   </si>
   <si>
     <t>SSP2-4.5, a moderate emissions scenario</t>
+  </si>
+  <si>
+    <t>Cascading impacts across systems and regions.</t>
   </si>
 </sst>
 </file>
@@ -709,13 +709,13 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -735,13 +735,13 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" t="s">
         <v>78</v>
       </c>
-      <c r="D4" t="s">
-        <v>79</v>
-      </c>
       <c r="F4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -784,7 +784,7 @@
         <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -1371,7 +1371,10 @@
         <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>79</v>
+      </c>
+      <c r="F31" t="s">
+        <v>63</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
@@ -1391,10 +1394,13 @@
         <v>2</v>
       </c>
       <c r="C32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" t="s">
         <v>57</v>
       </c>
-      <c r="D32" t="s">
-        <v>58</v>
+      <c r="F32" t="s">
+        <v>63</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
@@ -1414,10 +1420,13 @@
         <v>3</v>
       </c>
       <c r="C33" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" t="s">
         <v>59</v>
       </c>
-      <c r="D33" t="s">
-        <v>60</v>
+      <c r="F33" t="s">
+        <v>63</v>
       </c>
       <c r="G33" t="s">
         <v>13</v>
@@ -1431,74 +1440,74 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s">
         <v>61</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" t="s">
         <v>62</v>
       </c>
-      <c r="C34" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="F34" t="s">
         <v>63</v>
-      </c>
-      <c r="F34" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" t="s">
         <v>65</v>
-      </c>
-      <c r="C35" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" t="s">
         <v>67</v>
-      </c>
-      <c r="C36" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" t="s">
         <v>69</v>
-      </c>
-      <c r="C37" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B38" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" t="s">
         <v>71</v>
-      </c>
-      <c r="C38" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B39" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" t="s">
         <v>73</v>
-      </c>
-      <c r="C39" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Figures.xlsx
+++ b/Figures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andres/Documents/GitHub/AMOC_Figures_Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5EB3F1-6890-6949-8B25-54AD8B4DB4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1C84CE-3D6B-FA44-8993-47BDAE35DC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="920" yWindow="3500" windowWidth="29200" windowHeight="14120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -326,10 +326,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -653,874 +651,1000 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="136" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="G5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
         <v>1</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F6" t="s">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
+      <c r="G6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>2</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8">
+      <c r="A8" s="1">
         <v>2</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>2</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9">
+      <c r="A9" s="1">
         <v>2</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>3</v>
       </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10">
+      <c r="A10" s="1">
         <v>2</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>4</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>2</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>5</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12">
+      <c r="A12" s="1">
         <v>2</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>6</v>
       </c>
-      <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13">
+      <c r="A13" s="1">
         <v>2</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>7</v>
       </c>
-      <c r="C13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14">
+      <c r="A14" s="1">
         <v>3</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15">
+      <c r="A15" s="1">
         <v>3</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>2</v>
       </c>
-      <c r="C15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="E15" s="1"/>
+      <c r="F15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G15" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
+      <c r="G15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16">
+      <c r="A16" s="1">
         <v>3</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="1">
         <v>3</v>
       </c>
-      <c r="C16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="E16" s="1"/>
+      <c r="F16" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G16" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17">
+      <c r="G16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
         <v>3</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="1">
         <v>4</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G17" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18">
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
         <v>3</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1">
         <v>5</v>
       </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="C18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19">
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
         <v>3</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="1">
         <v>6</v>
       </c>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20">
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
         <v>3</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="1">
         <v>7</v>
       </c>
-      <c r="C20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="C20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G20" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21">
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
         <v>3</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="1">
         <v>8</v>
       </c>
-      <c r="C21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="E21" s="1"/>
+      <c r="F21" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22">
+      <c r="G21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
         <v>4</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="1">
         <v>1</v>
       </c>
-      <c r="C22" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G22" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23">
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
         <v>4</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="1">
         <v>2</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24">
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
         <v>4</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="1">
         <v>3</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G24" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25">
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
         <v>4</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="1">
         <v>4</v>
       </c>
-      <c r="C25" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="C25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G25" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26">
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
         <v>4</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="1">
         <v>5</v>
       </c>
-      <c r="C26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="C26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G26" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27">
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
         <v>4</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="1">
         <v>6</v>
       </c>
-      <c r="C27" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="C27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G27" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28">
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
         <v>5</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <v>1</v>
       </c>
-      <c r="C28" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="C28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F28" t="s">
+      <c r="E28" s="1"/>
+      <c r="F28" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G28" t="s">
-        <v>13</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="G28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29">
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
         <v>5</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="1">
         <v>2</v>
       </c>
-      <c r="C29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="C29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G29" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30">
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
         <v>5</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="1">
         <v>3</v>
       </c>
-      <c r="C30" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="C30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G30" t="s">
-        <v>13</v>
-      </c>
-      <c r="H30" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31">
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
         <v>6</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="1">
         <v>1</v>
       </c>
-      <c r="C31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="C31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F31" t="s">
+      <c r="E31" s="1"/>
+      <c r="F31" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G31" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32">
+      <c r="G31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
         <v>6</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="1">
         <v>2</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F32" t="s">
+      <c r="E32" s="1"/>
+      <c r="F32" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33">
+      <c r="G32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
         <v>6</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="1">
         <v>3</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F33" t="s">
+      <c r="E33" s="1"/>
+      <c r="F33" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G33" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="G33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F34" t="s">
+      <c r="E34" s="1"/>
+      <c r="F34" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>76</v>
       </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
